--- a/NGS_comments_automation.xlsx
+++ b/NGS_comments_automation.xlsx
@@ -1,30 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\MOLECULAR DIAGNOSTICS\Clinical Scientists\Training Records\Brittany\Haemonc NGS\Comments streamlit version\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{498CB4EB-B985-43D2-A12B-9DD51CB25125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F3084E0-ECD2-4D86-9160-02AC6E5C935D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="23355" windowHeight="14475" firstSheet="2" activeTab="2" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
+    <workbookView xWindow="28680" yWindow="-1860" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
   </bookViews>
   <sheets>
     <sheet name="AML" sheetId="1" r:id="rId1"/>
     <sheet name="MDS" sheetId="2" r:id="rId2"/>
     <sheet name="MPN" sheetId="3" r:id="rId3"/>
-    <sheet name="Myeloma" sheetId="8" r:id="rId4"/>
-    <sheet name="B lymphoid" sheetId="4" r:id="rId5"/>
-    <sheet name="T lymphoid" sheetId="17" r:id="rId6"/>
-    <sheet name="CLL" sheetId="14" r:id="rId7"/>
-    <sheet name="ALL" sheetId="6" r:id="rId8"/>
-    <sheet name="Histiocytic disorders" sheetId="16" r:id="rId9"/>
-    <sheet name="Caveats" sheetId="11" r:id="rId10"/>
-    <sheet name="Panel" sheetId="12" r:id="rId11"/>
-    <sheet name="CNV" sheetId="13" r:id="rId12"/>
+    <sheet name="MPN limited" sheetId="18" r:id="rId4"/>
+    <sheet name="Myeloma" sheetId="8" r:id="rId5"/>
+    <sheet name="B lymphoid" sheetId="4" r:id="rId6"/>
+    <sheet name="T lymphoid" sheetId="17" r:id="rId7"/>
+    <sheet name="CLL" sheetId="14" r:id="rId8"/>
+    <sheet name="ALL" sheetId="6" r:id="rId9"/>
+    <sheet name="Histiocytic disorders" sheetId="16" r:id="rId10"/>
+    <sheet name="Caveats" sheetId="11" r:id="rId11"/>
+    <sheet name="Panel" sheetId="12" r:id="rId12"/>
+    <sheet name="CNV" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -85,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="439">
   <si>
     <t>Gene</t>
   </si>
@@ -124,9 +125,6 @@
   </si>
   <si>
     <t>Genes</t>
-  </si>
-  <si>
-    <t>MPN limited</t>
   </si>
   <si>
     <t>CLL</t>
@@ -234,9 +232,6 @@
   </si>
   <si>
     <t>Del(11q), has been detected in 10 to 20% of CLL patients, and removes the ATM gene (WHO 5th edition).</t>
-  </si>
-  <si>
-    <t>CNV analysis detected multiple copy number gains and/or copy number losses, suggestive of genomic complexity. Genomic complexity is an independent negative prognostic marker in CLL, particularly for ≥ 5 copy number aberrations in TP53 wildtype cases (WHO 5th ed, ERIC 2022).</t>
   </si>
   <si>
     <t>Approximately 10% of CLL cases with trisomy 12 also have trisomy 19 and are associated with mutated IGHV genes in CLL  (PMID: 17593029)</t>
@@ -932,11 +927,6 @@
   </si>
   <si>
     <t>NF1 mutations are reported in MDS, please refer to the IPSS-M for prognostic indications (DOI: 10.1056/EVIDoa2200008).</t>
-  </si>
-  <si>
-    <t>NPM1 mutations are reported in MDS, please refer to the IPSS-M for prognostic indications (DOI: 10.1056/EVIDoa2200008).
-Note: According to the WHO 5th Edition, the presence of an NPM1 mutation is considered an AML-defining genetic abnormality irrespective of blast percentage. Cases with morphological features overlapping with myelodysplastic neoplasms or myelodysplastic/myeloproliferative neoplasms (including CMML) should be classified as AML with NPM1 mutation when the mutation is detected at presentation.
-In contrast, under the ICC 2022, a diagnosis of AML with mutated NPM1 requires ≥10% blasts.</t>
   </si>
   <si>
     <t>NRAS mutations are reported in MDS, please refer to the IPSS-M for prognostic indications (DOI: 10.1056/EVIDoa2200008).
@@ -1668,12 +1658,6 @@
 </t>
   </si>
   <si>
-    <t>No pathogenic/likely pathogenic variants were detected in the regions analysed within the ARID1A, ATM, BCL2, BRAF, BTK, CARD11, CCND3, CD79B, CREBBP, CXCR4, DNMT3A, EP300, EZH2, FOXO1, FYN, HRAS, ID3, IDH2, IRF4, JAK1, JAK3, KLF2, KRAS, MAP2K1, MEF2B, MYD88, NOTCH1, NOTCH2, NRAS, PDCD1LG2, PLCG1, PLCG2, POT1, RHOA, SETD2, STAT3, STAT5B, STAT6, TCF3, TET2, TNFAIP3, TNFRSF14, TP53, VAV1 genes.</t>
-  </si>
-  <si>
-    <t>No pathogenic/likely pathogenic variants were detected in the regions analysed within the ATM, BCL2, BIRC3, BTK, NOTCH1, PLCG2, SF3B1, TP53 genes.</t>
-  </si>
-  <si>
     <t>ALLv4.0</t>
   </si>
   <si>
@@ -1698,13 +1682,7 @@
     <t>Histiocytosisv4.0</t>
   </si>
   <si>
-    <t>No pathogenic/likely pathogenic variants were detected in the regions analysed within the ARAF, BRAF, CSF1R, ERBB3, HRAS, KRAS, MAP2K1, MAP3K1, NRAS, PIK3CA, PIK3CD genes.</t>
-  </si>
-  <si>
     <t>AMLandALLv4.0</t>
-  </si>
-  <si>
-    <t>No pathogenic/likely pathogenic variants were detected in the regions analysed within the ABL1, ANKRD26, ASXL1, BCL2, BCOR, BCORL1, CALR, CBFB, CBL, CEBPA, CSF3R, CUX1, DDX41, DNMT3A, ETNK1, ETV6, EZH2, FBXW7, FLT3, GATA1, GATA2, GNB1, HRAS, IDH1, IDH2, IKZF1, JAK2, KIT, KMT2A, KRAS, MPL, MYC, NF1, NFE2, NPM1, NOTCH1, NRAS, NUDT15, PAX5, PHF6, PPM1D, PRPF8, PTEN, PTPN11, RAD21, RHOA, RUNX1, SETBP1, SF1, SF3B1, SH2B3, SMC3, SRSF2, STAG2, STAT3, STAT5B, TET2, TP53, TPMT, U2AF1, UBA1, WT1, ZRSR2 genes.</t>
   </si>
   <si>
     <t>No pertinent (tier 1 or tier 2) copy number aberrations were detected in this sample. 
@@ -1726,9 +1704,6 @@
     <t>Please note the quantity of DNA obtained from this sample did not meet the quality criteria for NGS testing. Please send a repeat sample, if possible.</t>
   </si>
   <si>
-    <t>Copy number analysis has not been performed, as it has only been validated for samples with ≥40% neoplastic content.</t>
-  </si>
-  <si>
     <t>&lt;40% tumour content CNV</t>
   </si>
   <si>
@@ -1754,9 +1729,6 @@
   </si>
   <si>
     <t>CNV analysis by NGS was not performed for this sample due to high genome wide disruption, which prevented reliable assessment of copy number variation.</t>
-  </si>
-  <si>
-    <t>The neoplastic cell content of this sample is not available. The presence of low-level variants cannot be excluded. This assay has been validated to detect small variants present at ≥1% mutant DNA in a background of wild-type DNA. Copy number analysis has not been performed as it has only been validated for samples with ≥40% neoplastic content.</t>
   </si>
   <si>
     <t>STAT5B variants are reported in a number of T lymphoid malignancies (WHO 5th Edition).
@@ -1765,9 +1737,6 @@
   </si>
   <si>
     <t>NGS negative tumour content unknown</t>
-  </si>
-  <si>
-    <t>Please review the tumour content of the sample for interpretation of this result. Low tumour content reduces the sensitivity of NGS and it may result in false negative findings. This assay has been validated to detect as little as 1% mutant DNA in a background of wild type DNA. Copy number analysis has not been performed as it has only been validated for samples with ≥40% neoplastic content.</t>
   </si>
   <si>
     <t>Del(13q) DLEU2/miR15</t>
@@ -1807,13 +1776,6 @@
     <t>Failed</t>
   </si>
   <si>
-    <t>No pathogenic/likely pathogenic variants were detected in the regions analysed within the ABL1, ETV6, FBXW7, HRAS, IKZF1, KRAS, NOTCH1, NRAS, PAX5, PTEN, TP53  genes.
-For children:
-Please note that copy number variation (CNV) and structural variation (SV) analyses are not performed in cases of lymphoblastic leukaemia (ALL). Please refer to SNP array, RNA NGS and cytogenetics report for findings where available.
-For adults:
-Please note that copy number variation (CNV) and structural variation (SV) analyses are not performed in cases of lymphoblastic leukaemia (ALL). Please refer to RNA NGS and cytogenetics report for findings where available.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mutations in ETNK1 and/or SETBP1 are most frequently reported in MDS/MPN N (WHO 5th Edition).
 ETNK1 mutations have been reported in myeloid malignancies, including MDS/MPN N, CMML and SM with eosinophilia (DOI: 10.1038/s41467-020-19721-w).
 ETNK1 mutations have been reported rarely in CNL (WHO 5th Edition).
@@ -1821,22 +1783,6 @@
 Old - ETNK1 N244S (ENST00000671733.1)
 New - ETNK1 c.724A&gt;G p.Asn155Ser (ENST00000266517.9) (NM_018638.5)
 </t>
-  </si>
-  <si>
-    <t>Analysis on CD138+ cells:
-No pathogenic/likely pathogenic variants were detected in the regions analysed within the BRAF, DIS3, TENT5C, IRF4, KRAS, NRAS, TP53 genes.</t>
-  </si>
-  <si>
-    <t>No pathogenic/likely pathogenic variants were detected in the regions analysed within the JAK2, CALR, MPL, CSF3R and KIT genes.
-Absence of JAK2 V617F and JAK2 exon 12, MPL exon 10 and CALR exon 9 pathogenic variants does not exclude a myeloproliferative neoplasm. JAK2 (V617F/exon 12), MPL exon 10 or CALR exon 9 pathogenic variants have been reported to be present in &gt;97% of cases of polycythaemia vera and approximately 90% of cases of primary myelofibrosis and essential thrombocythaemia.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No pathogenic/likely pathogenic variants were detected in the regions analysed within the ARID1A, ATM, BCL2, BRAF, BTK, CARD11, CCND3, CD79B, CREBBP, CXCR4, EP300, EZH2, FOXO1, HRAS, ID3, JAK1, JAK3, KLF2, KRAS, MAP2K1, MEF2B, MYD88, NOTCH1, NOTCH2, NRAS, PDCD1LG2, PLCG2, STAT6, TCF3, TNFAIP3, TNFRSF14, TP53 genes.
-The analysis did not find copy number alterations supporting copy number loss of 1p, 6q, 7q or copy number gain of 3,12, 18, however, please note this has not been clinically validated so it should be interpreted with caution. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">No pathogenic/likely pathogenic variants were detected in the regions analysed within the ATM, CARD11, DNMT3A, FYN, IDH2, IRF4, JAK1, JAK3, PLCG1, POT1, RHOA, SETD2, STAT3, STAT5B, TET2, TP53, VAV1 genes.
-The analysis did not find copy number alterations supporting copy number loss of 9p (containing CDKN2A), 10q (containing PTEN), 11, 17q or copy number gain of 3,12, 18, however, please note this has not been clinically validated so it should be interpreted with caution. </t>
   </si>
   <si>
     <t xml:space="preserve">Somatic IDH2 mutations occur in approximately 12% of AML cases, with increased prevalence in elderly patients (DOI: 10.1038/s41408-021-00497-1). 
@@ -1953,14 +1899,69 @@
 Recurrent exon 13 tandem duplications (TD) in UBTF have emerged as a major subtype-defining genomic alteration in paediatric AML that is associated with poor prognosis and has also recently been reported in 1.2% of all individuals over 18 years of age (DOI: 10.1182/blood.2023021359).</t>
   </si>
   <si>
-    <t>No pathogenic/likely pathogenic variants were detected in the regions analysed within the ABL1, ANKRD26, ASXL1, BCL2, BCOR, BCORL1, CALR, CBFB, CBL, CEBPA, CSF3R, CUX1, DDX41, DNMT3A, ETNK1, ETV6, EZH2, FLT3, GATA1, GATA2, GNB1, HRAS, IDH1, IDH2, IKZF1, JAK2, KIT, KMT2A, KRAS, MPL, MYC, NF1, NFE2, NPM1, NRAS, PHF6, PPM1D, PRPF8, PTPN11, RAD21, RHOA, RUNX1, SETBP1, SF1, SF3B1, SH2B3, SMC3, SRSF2, STAG2, STAT3, STAT5B, TET2, TP53, UBA1, U2AF1, WT1, ZRSR2  genes.</t>
+    <t>MPNlimitedv3.0</t>
+  </si>
+  <si>
+    <t>NPM1 mutations are reported in MDS, please refer to the IPSS-M for prognostic indications (DOI: 10.1056/EVIDoa2200008).
+Note: According to the WHO 5th Edition, the presence of an NPM1 mutation is considered an AML-defining genetic abnormality irrespective of blast percentage. Cases with morphological features overlapping with myelodysplastic neoplasms or myelodysplastic/myeloproliferative neoplasms (including CMML) should be classified as AML with NPM1 mutation when the mutation is detected at presentation.
+In contrast, under the ICC 2022, a diagnosis of AML with mutated NPM1 requires greater than or equal to 10% blasts.</t>
+  </si>
+  <si>
+    <t>Please review the tumour content of the sample for interpretation of this result. Low tumour content reduces the sensitivity of NGS and it may result in false negative findings. This assay has been validated to detect as little as 1% mutant DNA in a background of wild type DNA. Copy number analysis has not been performed as it has only been validated for samples with greater than or equal to 40% neoplastic content.</t>
+  </si>
+  <si>
+    <t>The neoplastic cell content of this sample is not available. The presence of low-level variants cannot be excluded. This assay has been validated to detect small variants present at greater than or equal to 1% mutant DNA in a background of wild-type DNA. Copy number analysis has not been performed as it has only been validated for samples with greater than or equal to 40% neoplastic content.</t>
+  </si>
+  <si>
+    <t>Copy number analysis has not been performed, as it has only been validated for samples with greater than or equal to 40% neoplastic content.</t>
+  </si>
+  <si>
+    <t>CNV analysis detected multiple copy number gains and/or copy number losses, suggestive of genomic complexity. Genomic complexity is an independent negative prognostic marker in CLL, particularly for greater than or equal to  5 copy number aberrations in TP53 wildtype cases (WHO 5th ed, ERIC 2022).</t>
+  </si>
+  <si>
+    <t>No oncogenic/likely oncogenic variants were detected in the regions analysed within the JAK2, CALR, MPL, CSF3R and KIT genes.
+Absence of JAK2 V617F and JAK2 exon 12, MPL exon 10 and CALR exon 9 oncogenic variants does not exclude a myeloproliferative neoplasm. JAK2 (V617F/exon 12), MPL exon 10 or CALR exon 9 oncogenic variants have been reported to be present in &gt;97% of cases of polycythaemia vera and approximately 90% of cases of primary myelofibrosis and essential thrombocythaemia.</t>
+  </si>
+  <si>
+    <t>No oncogenic/likely oncogenic variants were detected in the regions analysed within the ABL1, ANKRD26, ASXL1, BCL2, BCOR, BCORL1, CALR, CBFB, CBL, CEBPA, CSF3R, CUX1, DDX41, DNMT3A, ETNK1, ETV6, EZH2, FLT3, GATA1, GATA2, GNB1, HRAS, IDH1, IDH2, IKZF1, JAK2, KIT, KMT2A, KRAS, MPL, MYC, NF1, NFE2, NPM1, NRAS, PHF6, PPM1D, PRPF8, PTPN11, RAD21, RHOA, RUNX1, SETBP1, SF1, SF3B1, SH2B3, SMC3, SRSF2, STAG2, STAT3, STAT5B, TET2, TP53, UBA1, U2AF1, WT1, ZRSR2  genes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No oncogenic/likely oncogenic variants were detected in the regions analysed within the ARID1A, ATM, BCL2, BRAF, BTK, CARD11, CCND3, CD79B, CREBBP, CXCR4, EP300, EZH2, FOXO1, HRAS, ID3, JAK1, JAK3, KLF2, KRAS, MAP2K1, MEF2B, MYD88, NOTCH1, NOTCH2, NRAS, PDCD1LG2, PLCG2, STAT6, TCF3, TNFAIP3, TNFRSF14, TP53 genes.
+The analysis did not find copy number alterations supporting copy number loss of 1p, 6q, 7q or copy number gain of 3,12, 18, however, please note this has not been clinically validated so it should be interpreted with caution. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">No oncogenic/likely oncogenic variants were detected in the regions analysed within the ATM, CARD11, DNMT3A, FYN, IDH2, IRF4, JAK1, JAK3, PLCG1, POT1, RHOA, SETD2, STAT3, STAT5B, TET2, TP53, VAV1 genes.
+The analysis did not find copy number alterations supporting copy number loss of 9p (containing CDKN2A), 10q (containing PTEN), 11, 17q or copy number gain of 3,12, 18, however, please note this has not been clinically validated so it should be interpreted with caution. </t>
+  </si>
+  <si>
+    <t>No oncogenic/likely oncogenic variants were detected in the regions analysed within the ARID1A, ATM, BCL2, BRAF, BTK, CARD11, CCND3, CD79B, CREBBP, CXCR4, DNMT3A, EP300, EZH2, FOXO1, FYN, HRAS, ID3, IDH2, IRF4, JAK1, JAK3, KLF2, KRAS, MAP2K1, MEF2B, MYD88, NOTCH1, NOTCH2, NRAS, PDCD1LG2, PLCG1, PLCG2, POT1, RHOA, SETD2, STAT3, STAT5B, STAT6, TCF3, TET2, TNFAIP3, TNFRSF14, TP53, VAV1 genes.</t>
+  </si>
+  <si>
+    <t>No oncogenic/likely oncogenic variants were detected in the regions analysed within the ATM, BCL2, BIRC3, BTK, NOTCH1, PLCG2, SF3B1, TP53 genes.</t>
+  </si>
+  <si>
+    <t>Analysis on CD138+ cells:
+No oncogenic/likely oncogenic variants were detected in the regions analysed within the BRAF, DIS3, TENT5C, IRF4, KRAS, NRAS, TP53 genes.</t>
+  </si>
+  <si>
+    <t>No oncogenic/likely oncogenic variants were detected in the regions analysed within the ABL1, ETV6, FBXW7, HRAS, IKZF1, KRAS, NOTCH1, NRAS, PAX5, PTEN, TP53  genes.
+For children:
+Please note that copy number variation (CNV) and structural variation (SV) analyses are not performed in cases of lymphoblastic leukaemia (ALL). Please refer to SNP array, RNA NGS and cytogenetics report for findings where available.
+For adults:
+Please note that copy number variation (CNV) and structural variation (SV) analyses are not performed in cases of lymphoblastic leukaemia (ALL). Please refer to RNA NGS and cytogenetics report for findings where available.</t>
+  </si>
+  <si>
+    <t>No oncogenic/likely oncogenic variants were detected in the regions analysed within the ARAF, BRAF, CSF1R, ERBB3, HRAS, KRAS, MAP2K1, MAP3K1, NRAS, PIK3CA, PIK3CD genes.</t>
+  </si>
+  <si>
+    <t>No oncogenic/likely oncogenic variants were detected in the regions analysed within the ABL1, ANKRD26, ASXL1, BCL2, BCOR, BCORL1, CALR, CBFB, CBL, CEBPA, CSF3R, CUX1, DDX41, DNMT3A, ETNK1, ETV6, EZH2, FBXW7, FLT3, GATA1, GATA2, GNB1, HRAS, IDH1, IDH2, IKZF1, JAK2, KIT, KMT2A, KRAS, MPL, MYC, NF1, NFE2, NPM1, NOTCH1, NRAS, NUDT15, PAX5, PHF6, PPM1D, PRPF8, PTEN, PTPN11, RAD21, RHOA, RUNX1, SETBP1, SF1, SF3B1, SH2B3, SMC3, SRSF2, STAG2, STAT3, STAT5B, TET2, TP53, TPMT, U2AF1, UBA1, WT1, ZRSR2 genes.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2003,12 +2004,6 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Cambria"/>
-      <family val="1"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2030,7 +2025,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2082,9 +2077,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2462,7 +2454,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="105.75" x14ac:dyDescent="0.25">
@@ -2470,10 +2462,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C2" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
       <c r="F2" s="6"/>
     </row>
@@ -2482,10 +2474,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C3" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -2493,10 +2485,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C4" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="105" x14ac:dyDescent="0.2">
@@ -2504,505 +2496,505 @@
         <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C6" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C7" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C8" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C9" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C10" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C11" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="255" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C12" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="167.25" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C13" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="90" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C14" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="180" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C15" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="105" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C16" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="333" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C17" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="120" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C18" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="120" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C19" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C20" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C21" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>414</v>
+        <v>399</v>
       </c>
       <c r="C22" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C23" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="195" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="C24" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="165" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C25" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="165" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C26" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C27" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C28" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="285" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C29" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="165" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C30" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C31" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C32" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C33" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C34" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C35" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="345" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C36" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C37" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C38" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C39" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C40" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="195" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C41" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="150" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C42" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C43" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C44" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C45" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C46" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C47" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>437</v>
+        <v>422</v>
       </c>
       <c r="C48" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="C49" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C50" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
@@ -3010,10 +3002,156 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="47" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;CIndex: GEN-DOC 23 | Title: Additional interpretation comments for haemonc NGS | Version: 3.1</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D047D86-2DA7-40D0-AE18-DD845C71F766}">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="10.109375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="74.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.88671875" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="105" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="C2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>328</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C3" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="120" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C4" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="45" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="C5" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="45" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="C6" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="C7" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="C8" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C9" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="C10" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="C11" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="C12" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B13" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="74" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;CIndex: GEN-DOC 23 | Title: Additional interpretation comments for haemonc NGS | Version: 3.1</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71C181D1-9A1A-4B63-974F-1376CEB759F1}">
   <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -3025,138 +3163,142 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>398</v>
+        <v>425</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>395</v>
+        <v>426</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>407</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>406</v>
+        <v>397</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>396</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="64" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;CIndex: GEN-DOC 23 | Title: Additional interpretation comments for haemonc NGS | Version: 3.1</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D59AC4A2-C3A3-47B0-98AB-490EB46276E7}">
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -3175,90 +3317,94 @@
     </row>
     <row r="2" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>423</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>412</v>
+        <v>431</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>413</v>
+        <v>432</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>366</v>
+        <v>433</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>367</v>
+        <v>434</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>410</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>408</v>
+        <v>436</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>376</v>
+        <v>437</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>378</v>
+        <v>438</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="68" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;CIndex: GEN-DOC 23 | Title: Additional interpretation comments for haemonc NGS | Version: 3.1</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A9F24A3-EA82-4A17-B915-0BA86DD79F59}">
   <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -3270,304 +3416,308 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="225" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>49</v>
+        <v>428</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A18" s="16" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A19" s="16" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A20" s="16" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="16" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A22" s="16" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A23" s="18" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A24" s="18" t="s">
+        <v>349</v>
+      </c>
+      <c r="B24" s="17" t="s">
         <v>352</v>
       </c>
-      <c r="B24" s="17" t="s">
-        <v>355</v>
-      </c>
       <c r="C24" s="15" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="18" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A26" s="18" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A27" s="16" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup scale="57" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;CIndex: GEN-DOC 23 | Title: Additional interpretation comments for haemonc NGS | Version: 3.1</oddFooter>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -3590,7 +3740,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -3598,10 +3748,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -3609,10 +3759,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -3620,10 +3770,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3631,528 +3781,532 @@
         <v>7</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="270" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="120" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="270" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="120" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>425</v>
+        <v>410</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>216</v>
+        <v>424</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="369" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="165" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="165" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="210" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>422</v>
+        <v>407</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="52" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;CIndex: GEN-DOC 23 | Title: Additional interpretation comments for haemonc NGS | Version: 3.1</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -4175,7 +4329,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -4183,10 +4337,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="285" x14ac:dyDescent="0.2">
@@ -4194,10 +4348,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4205,10 +4359,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -4216,500 +4370,580 @@
         <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="120" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="135" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="270" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="150" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="180" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="135" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="240" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>425</v>
+        <v>410</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="165" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="270" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="195" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="195" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="270" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="180" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="170.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="135" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="5" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="195" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="58" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;CIndex: GEN-DOC 23 | Title: Additional interpretation comments for haemonc NGS | Version: 3.1</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{830946D8-DBD8-46E8-BD30-2ABE1F9D3A2D}">
+  <dimension ref="A2:C6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="98.21875" customWidth="1"/>
+    <col min="3" max="3" width="25.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" ht="120" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="60" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="240" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="105" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="409.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>402</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="61" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;CIndex: GEN-DOC 23 | Title: Additional interpretation comments for haemonc NGS | Version: 3.1</oddFooter>
+  </headerFooter>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="1" max="5" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F97093D-988E-4644-B83D-8D3E695F3E69}">
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -4728,7 +4962,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4736,85 +4970,89 @@
         <v>10</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C2" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C3" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C4" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
       <c r="F5" s="6"/>
     </row>
     <row r="6" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C6" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C7" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C8" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="74" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;CIndex: GEN-DOC 23 | Title: Additional interpretation comments for haemonc NGS | Version: 3.1</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD634E30-2FF4-4CAE-85E8-877093FDD5DC}">
   <dimension ref="A1:C30"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -4833,7 +5071,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4841,10 +5079,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C2" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -4852,10 +5090,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C3" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -4863,10 +5101,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C4" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4874,293 +5112,297 @@
         <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C6" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C7" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C8" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C9" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C10" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C11" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C12" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C13" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C14" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C15" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C16" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C17" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C18" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C19" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C20" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="150" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>415</v>
+        <v>400</v>
       </c>
       <c r="C21" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C22" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C23" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C24" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C25" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C26" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C27" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C28" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="C29" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="240" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C30" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="56" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;CIndex: GEN-DOC 23 | Title: Additional interpretation comments for haemonc NGS | Version: 3.1</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F86327E5-C3AE-4491-932D-1E8E8290018D}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -5176,183 +5418,187 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C2" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C3" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C4" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C6" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C7" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C8" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C9" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C10" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C11" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C12" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="180" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C13" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="C14" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C15" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="C16" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="79" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;CIndex: GEN-DOC 23 | Title: Additional interpretation comments for haemonc NGS | Version: 3.1</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F0E87CA-7F9D-46CA-9D15-8D7338F0E910}">
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -5369,7 +5615,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -5377,10 +5623,10 @@
         <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C2" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="45" x14ac:dyDescent="0.2">
@@ -5388,10 +5634,10 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C3" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
       <c r="D3" s="11"/>
     </row>
@@ -5400,74 +5646,78 @@
         <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C4" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="405" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="C5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="C6" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C7" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C8" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="90" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C9" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup scale="35" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;CIndex: GEN-DOC 23 | Title: Additional interpretation comments for haemonc NGS | Version: 3.1</oddFooter>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD65405E-7754-49F8-8BF9-5636ED341878}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -5486,7 +5736,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -5494,259 +5744,125 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C2" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C3" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="C4" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="150" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C6" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="C7" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="C8" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="C9" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="150" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="C10" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="C11" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="165" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>434</v>
+        <v>419</v>
       </c>
       <c r="C12" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D047D86-2DA7-40D0-AE18-DD845C71F766}">
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="10.109375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="74.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="105" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>257</v>
-      </c>
-      <c r="C2" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>331</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="C3" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="120" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="C4" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="45" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="C5" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="45" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="C6" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="C7" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="C8" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="C9" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="C10" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="C11" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="C12" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B13" s="4"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="51" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;CIndex: GEN-DOC 23 | Title: Additional interpretation comments for haemonc NGS | Version: 3.1</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>